--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0007.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0007.xlsx
@@ -1840,12 +1840,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Inga flyttar</t>
+          <t>Fler invandrar i arbetsålder</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Alla blir yngre</t>
+          <t>Fler arbetar längre innan pension</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Inga äldre alls</t>
+          <t>Oförändrad åldersstruktur</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Alla är i pension</t>
+          <t>Fler unga och färre äldre</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Bara export</t>
+          <t>Exportintäkter</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>För att stoppa utbildning</t>
+          <t>För att hålla skattenivån stabil</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>För att minska rättigheter</t>
+          <t>För att undvika stora budgetunderskott</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>För att avskaffa kommuner</t>
+          <t>För att minska statens upplåning</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Endast sporttjänster</t>
+          <t>Infrastruktur och vägunderhåll</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Endast turism</t>
+          <t>Kultur- och fritidsverksamhet</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Endast militärövningar</t>
+          <t>Näringslivsstöd och exportfrämjande</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Utveckling utan miljöhänsyn</t>
+          <t>Utveckling som prioriterar ekonomi över miljö</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Bara ekonomisk tillväxt</t>
+          <t>Utveckling som fokuserar enbart på miljön</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Endast lokal skogsvård</t>
+          <t>Utveckling som främst gäller lokala projekt</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Endast militär, handel, sport</t>
+          <t>Miljö, teknologi och säkerhet</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Skog, sjö, snö</t>
+          <t>Ekonomi, handel och konkurrenskraft</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Kyrka, kung, krig</t>
+          <t>Kultur, tradition och religion</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Öka extrem fattigdom</t>
+          <t>Öka konsumtionen utan hänsyn till miljön</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Förbjuda utbildning</t>
+          <t>Sänka miljökrav för industrin</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Bygga fler fängelser</t>
+          <t>Prioritera kortsiktig tillväxt</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Öka ojämlikheter</t>
+          <t>Öka ekonomiska ojämlikheter</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Avskaffa miljöskydd</t>
+          <t>Minska miljökrav för industrin</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Öka avskogning</t>
+          <t>Öka resursuttaget från naturen</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Stoppa all handel</t>
+          <t>Öka tillväxt oavsett miljöeffekter</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Avskaffa skatter</t>
+          <t>Fokusera främst på ekonomisk tillväxt</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Förbjuda resor</t>
+          <t>Prioritera nationella intressen före globala</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Öka extrem fattigdom</t>
+          <t>Sänka skatter globalt</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Avskaffa energitillgång</t>
+          <t>Öka resursslöseri</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Stoppa utbildning</t>
+          <t>Stärka militär upprustning</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Finland har varit sämst i världen</t>
+          <t>Finland har varit bland de sämre i Europa</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Finland deltar inte</t>
+          <t>Finland har legat ungefär i mitten</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Finland har avbrutit arbetet</t>
+          <t>Finland har haft mycket varierande resultat</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot energi</t>
+          <t>Minskad ojämlikhet</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Ökad avskogning</t>
+          <t>Klimatneutralitet</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Stoppa all utbildning</t>
+          <t>Skydd av biologisk mångfald</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Minskad läskunnighet</t>
+          <t>Hållbara städer</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot energi</t>
+          <t>Rent vatten</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Ökad fattigdom</t>
+          <t>Klimatåtgärder</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Total energibrist</t>
+          <t>Anständiga arbetsvillkor</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot el</t>
+          <t>Rent vatten</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Endast ved</t>
+          <t>Hållbara städer</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Ökat slöseri</t>
+          <t>Minskade utsläpp</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot teknik</t>
+          <t>Ökad återvinning</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Mindre handel</t>
+          <t>Mer kollektivtrafik</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Konsumera mer och slänga mer</t>
+          <t>Återvinna och återanvända mer</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Sluta sortera avfall</t>
+          <t>Välja mer hållbara produkter</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Öka utsläpp</t>
+          <t>Minska energiförbrukningen i vardagen</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Öka fossila bränslen</t>
+          <t>Öka användningen av fossila bränslen i industrin</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Öka avskogning</t>
+          <t>Öka avskogningen i Finland och globalt</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Stoppa energieffektivitet</t>
+          <t>Stoppa energieffektivisering i byggnader och transporter</t>
         </is>
       </c>
       <c r="G28" s="14" t="n">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>De kan stoppas helt</t>
+          <t>De kan skjutas upp till senare</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>De är redan klara</t>
+          <t>De räcker att hålla nuvarande nivå</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>De är bara lokala</t>
+          <t>De kan lämnas till enskilda kommuner</t>
         </is>
       </c>
       <c r="G29" s="14" t="n">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Gör klimatet tropiskt</t>
+          <t>Ökar risken för värmeböljor</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>Stoppar all uppvärmning</t>
+          <t>Ger snabbare havsnivåhöjning än globalt</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>Tar bort all nederbörd</t>
+          <t>Gör vintrarna kortare och mildare</t>
         </is>
       </c>
       <c r="G30" s="14" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>Skåne</t>
+          <t>Nyland</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>Gotland</t>
+          <t>Österbotten</t>
         </is>
       </c>
       <c r="G31" s="14" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Inga effekter märks</t>
+          <t>Påverkan är liten jämfört med södra Finland</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>Bara städer drabbas</t>
+          <t>Förändringen märks främst i städer</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>Endast havet påverkas</t>
+          <t>Effekterna gäller mest havsområden</t>
         </is>
       </c>
       <c r="G32" s="14" t="n">
